--- a/cet4/result/48_钢琴女神_琴键上的逆袭之路/48_钢琴女神_琴键上的逆袭之路_学习版.xlsx
+++ b/cet4/result/48_钢琴女神_琴键上的逆袭之路/48_钢琴女神_琴键上的逆袭之路_学习版.xlsx
@@ -397,661 +397,647 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D45"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>October</v>
       </c>
       <c r="B2" t="str">
-        <v>October</v>
+        <v>/ɑːkˈtoʊbər/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>十月</v>
       </c>
-      <c r="D2" t="str">
-        <v>October(十月)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>hill</v>
       </c>
       <c r="B3" t="str">
-        <v>hill</v>
+        <v>/hɪl/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>小山</v>
       </c>
-      <c r="D3" t="str">
-        <v>hill(小山)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>grass</v>
       </c>
       <c r="B4" t="str">
-        <v>grass</v>
+        <v>/ɡræs/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D4" t="str">
         <v>草</v>
       </c>
-      <c r="D4" t="str">
-        <v>grass(草)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>keyboard</v>
       </c>
       <c r="B5" t="str">
-        <v>keyboard</v>
+        <v>/ˈkiːbɔːrd/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D5" t="str">
         <v>键盘</v>
       </c>
-      <c r="D5" t="str">
-        <v>keyboard(键盘)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>hour</v>
       </c>
       <c r="B6" t="str">
-        <v>hour</v>
+        <v>/ˈaʊər/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>小时</v>
       </c>
-      <c r="D6" t="str">
-        <v>hour(小时)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>legend</v>
       </c>
       <c r="B7" t="str">
-        <v>legend</v>
+        <v>/ˈledʒənd/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>传奇</v>
       </c>
-      <c r="D7" t="str">
-        <v>legend(传奇)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>optical</v>
       </c>
       <c r="B8" t="str">
-        <v>optical</v>
+        <v>/ˈɑːptɪkl/</v>
       </c>
       <c r="C8" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>光学的</v>
       </c>
-      <c r="D8" t="str">
-        <v>optical(光学的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>oral</v>
       </c>
       <c r="B9" t="str">
-        <v>oral</v>
+        <v>/ˈɔːrəl/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>口头的</v>
       </c>
-      <c r="D9" t="str">
-        <v>oral(口头的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>Europe</v>
       </c>
       <c r="B10" t="str">
-        <v>Europe</v>
+        <v>/ˈjʊrəp/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>欧洲</v>
       </c>
-      <c r="D10" t="str">
-        <v>Europe(欧洲)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>reed</v>
       </c>
       <c r="B11" t="str">
-        <v>reed</v>
+        <v>/riːd/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D11" t="str">
         <v>芦苇</v>
       </c>
-      <c r="D11" t="str">
-        <v>reed(芦苇)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>committee</v>
       </c>
       <c r="B12" t="str">
-        <v>committee</v>
+        <v>/kəˈmɪti/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>委员会</v>
       </c>
-      <c r="D12" t="str">
-        <v>committee(委员会)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>India</v>
       </c>
       <c r="B13" t="str">
-        <v>India</v>
+        <v>/ˈɪndiə/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>印度</v>
       </c>
-      <c r="D13" t="str">
-        <v>India(印度)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>computer</v>
       </c>
       <c r="B14" t="str">
-        <v>computer</v>
+        <v>/kəmˈpjuːtər/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>计算机</v>
       </c>
-      <c r="D14" t="str">
-        <v>computer(计算机)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>calculate</v>
       </c>
       <c r="B15" t="str">
-        <v>calculate</v>
+        <v>/ˈkælkjuleɪt/</v>
       </c>
       <c r="C15" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D15" t="str">
         <v>计算</v>
       </c>
-      <c r="D15" t="str">
-        <v>calculate(计算)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>meantime</v>
       </c>
       <c r="B16" t="str">
-        <v>meantime</v>
+        <v>/ˈmiːntaɪm/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./v./adv.</v>
+      </c>
+      <c r="D16" t="str">
         <v>同时</v>
       </c>
-      <c r="D16" t="str">
-        <v>meantime(同时)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>debate</v>
       </c>
       <c r="B17" t="str">
-        <v>debate</v>
+        <v>/dɪˈbeɪt/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D17" t="str">
         <v>辩论</v>
       </c>
-      <c r="D17" t="str">
-        <v>debate(辩论)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>limit</v>
       </c>
       <c r="B18" t="str">
-        <v>limit</v>
+        <v>/ˈlɪmɪt/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>限制</v>
       </c>
-      <c r="D18" t="str">
-        <v>limit(限制)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>speak</v>
       </c>
       <c r="B19" t="str">
-        <v>speak</v>
+        <v>/spiːk/</v>
       </c>
       <c r="C19" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>说话</v>
       </c>
-      <c r="D19" t="str">
-        <v>speak(说话)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>impress</v>
       </c>
       <c r="B20" t="str">
-        <v>impress</v>
+        <v>/ɪmˈpres/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D20" t="str">
         <v>给人印象</v>
       </c>
-      <c r="D20" t="str">
-        <v>impress(给人印象)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>purse</v>
       </c>
       <c r="B21" t="str">
-        <v>purse</v>
+        <v>/pɜːrs/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D21" t="str">
         <v>手提袋</v>
       </c>
-      <c r="D21" t="str">
-        <v>purse(手提袋)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>planet</v>
       </c>
       <c r="B22" t="str">
-        <v>planet</v>
+        <v>/ˈplænɪt/</v>
       </c>
       <c r="C22" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>行星</v>
       </c>
-      <c r="D22" t="str">
-        <v>planet(行星)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>funny</v>
       </c>
       <c r="B23" t="str">
-        <v>funny</v>
+        <v>/ˈfʌni/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>有趣的</v>
       </c>
-      <c r="D23" t="str">
-        <v>funny(有趣的)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>despite</v>
       </c>
       <c r="B24" t="str">
-        <v>despite</v>
+        <v>/dɪˈspaɪt/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./vt./prep.</v>
+      </c>
+      <c r="D24" t="str">
         <v>尽管</v>
       </c>
-      <c r="D24" t="str">
-        <v>despite(尽管)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>Jew</v>
       </c>
       <c r="B25" t="str">
-        <v>Jew</v>
+        <v/>
       </c>
       <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
         <v>犹太人</v>
       </c>
-      <c r="D25" t="str">
-        <v>Jew(犹太人)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>invention</v>
       </c>
       <c r="B26" t="str">
-        <v>invention</v>
+        <v>/ɪnˈvenʃn/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>发明</v>
       </c>
-      <c r="D26" t="str">
-        <v>invention(发明)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>intensity</v>
       </c>
       <c r="B27" t="str">
-        <v>intensity</v>
+        <v>/ɪnˈtensəti/</v>
       </c>
       <c r="C27" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>强度</v>
       </c>
-      <c r="D27" t="str">
-        <v>intensity(强度)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>specific</v>
       </c>
       <c r="B28" t="str">
-        <v>specific</v>
+        <v>/spəˈsɪfɪk/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>特定的</v>
       </c>
-      <c r="D28" t="str">
-        <v>specific(特定的)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>joint</v>
       </c>
       <c r="B29" t="str">
-        <v>joint</v>
+        <v>/dʒɔɪnt/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>共同的</v>
       </c>
-      <c r="D29" t="str">
-        <v>joint(共同的)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>spaceship</v>
       </c>
       <c r="B30" t="str">
-        <v>spaceship</v>
+        <v>/ˈspeɪsʃɪp/</v>
       </c>
       <c r="C30" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>宇宙飞船</v>
       </c>
-      <c r="D30" t="str">
-        <v>spaceship(宇宙飞船)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>observe</v>
       </c>
       <c r="B31" t="str">
-        <v>observe</v>
+        <v>/əbˈzɜːrv/</v>
       </c>
       <c r="C31" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D31" t="str">
         <v>观察</v>
       </c>
-      <c r="D31" t="str">
-        <v>observe(观察)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>framework</v>
       </c>
       <c r="B32" t="str">
-        <v>framework</v>
+        <v>/ˈfreɪmwɜːrk/</v>
       </c>
       <c r="C32" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>框架</v>
       </c>
-      <c r="D32" t="str">
-        <v>framework(框架)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>crazy</v>
       </c>
       <c r="B33" t="str">
-        <v>crazy</v>
+        <v>/ˈkreɪzi/</v>
       </c>
       <c r="C33" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D33" t="str">
         <v>疯狂</v>
       </c>
-      <c r="D33" t="str">
-        <v>crazy(疯狂)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>contrast</v>
       </c>
       <c r="B34" t="str">
-        <v>contrast</v>
+        <v>/ˈkɑːntræst/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D34" t="str">
         <v>对比</v>
       </c>
-      <c r="D34" t="str">
-        <v>contrast(对比)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>cultivate</v>
       </c>
       <c r="B35" t="str">
-        <v>cultivate</v>
+        <v>/ˈkʌltɪveɪt/</v>
       </c>
       <c r="C35" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D35" t="str">
         <v>培养</v>
       </c>
-      <c r="D35" t="str">
-        <v>cultivate(培养)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>wicked</v>
       </c>
       <c r="B36" t="str">
-        <v>wicked</v>
+        <v>/ˈwɪkɪd/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D36" t="str">
         <v>邪恶的</v>
       </c>
-      <c r="D36" t="str">
-        <v>wicked(邪恶的)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>practically</v>
       </c>
       <c r="B37" t="str">
-        <v>practically</v>
+        <v>/ˈpræktɪkli/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D37" t="str">
         <v>几乎</v>
       </c>
-      <c r="D37" t="str">
-        <v>practically(几乎)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>cheek</v>
       </c>
       <c r="B38" t="str">
-        <v>cheek</v>
+        <v>/tʃiːk/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D38" t="str">
         <v>面颊</v>
       </c>
-      <c r="D38" t="str">
-        <v>cheek(面颊)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>relate</v>
       </c>
       <c r="B39" t="str">
-        <v>relate</v>
+        <v>/rɪˈleɪt/</v>
       </c>
       <c r="C39" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D39" t="str">
         <v>叙述</v>
       </c>
-      <c r="D39" t="str">
-        <v>relate(叙述)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>retell</v>
       </c>
       <c r="B40" t="str">
-        <v>retell</v>
+        <v>/ˌriːˈtel/</v>
       </c>
       <c r="C40" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D40" t="str">
         <v>复述</v>
       </c>
-      <c r="D40" t="str">
-        <v>retell(复述)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>independent</v>
       </c>
       <c r="B41" t="str">
-        <v>independent</v>
+        <v>/ˌɪndɪˈpendənt/</v>
       </c>
       <c r="C41" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D41" t="str">
         <v>独立的</v>
       </c>
-      <c r="D41" t="str">
-        <v>independent(独立的)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>dim</v>
       </c>
       <c r="B42" t="str">
-        <v>dim</v>
+        <v>/dɪm/</v>
       </c>
       <c r="C42" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D42" t="str">
         <v>暗淡的</v>
       </c>
-      <c r="D42" t="str">
-        <v>dim(暗淡的)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>fish</v>
       </c>
       <c r="B43" t="str">
-        <v>fish</v>
+        <v>/fɪʃ/</v>
       </c>
       <c r="C43" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D43" t="str">
         <v>鱼</v>
       </c>
-      <c r="D43" t="str">
-        <v>fish(鱼)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>unite</v>
       </c>
       <c r="B44" t="str">
-        <v>unite</v>
+        <v>/juˈnaɪt/</v>
       </c>
       <c r="C44" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D44" t="str">
         <v>联合</v>
       </c>
-      <c r="D44" t="str">
-        <v>unite(联合)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>wholly</v>
       </c>
       <c r="B45" t="str">
-        <v>keyboard</v>
+        <v>/ˈhoʊlli/</v>
       </c>
       <c r="C45" t="str">
-        <v>键盘</v>
+        <v>v./adv.</v>
       </c>
       <c r="D45" t="str">
-        <v>keyboard(键盘)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>wholly</v>
-      </c>
-      <c r="C46" t="str">
         <v>完全地</v>
-      </c>
-      <c r="D46" t="str">
-        <v>wholly(完全地)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
   </ignoredErrors>
 </worksheet>
 </file>